--- a/results/05_modeling/ALL_summary.xlsx
+++ b/results/05_modeling/ALL_summary.xlsx
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7950423734525505</v>
+        <v>0.7914604990850014</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7803300993572464</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -539,10 +539,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7827777918629683</v>
+        <v>0.7830138502042437</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01875913928122007</v>
+        <v>0.01871381086800399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.127235033139615</v>
+        <v>0.1269362344566973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03014154041782496</v>
+        <v>0.03004361656874081</v>
       </c>
     </row>
     <row r="3">
@@ -612,35 +612,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7950423734525505</v>
+        <v>0.7914604990850014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.022906276421525</v>
+        <v>0.02177196714317657</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1921294753460224</v>
+        <v>0.1983569539223893</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04173421597947816</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>catboost</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7749474054256495</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.03936580996781421</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1888878873417933</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.04243115752518334</v>
+        <v>0.0418411119299538</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,25 +701,6 @@
       </c>
       <c r="E3" t="n">
         <v>0.02388852541442163</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>catboost</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.8193635515576089</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.02336584643623031</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3434883471190159</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.02827551939034324</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,16 +751,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7436214385423241</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01760657006189662</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.120027452177884</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01573639136082546</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="3">
@@ -808,35 +770,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7803300993572464</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02240333750729686</v>
+        <v>0.01830461526364529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1395906583983687</v>
+        <v>0.1305084174604524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01473078343769954</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>catboost</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7671712109690169</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.01692627218546185</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1433738303844752</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.01829340997248071</v>
+        <v>0.01322728173796852</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,16 +830,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="3">
@@ -906,35 +849,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01386992304711891</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>catboost</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7950796888840379</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.01567424950546039</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2118479711579678</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.02546531256831987</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -985,16 +909,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="3">
@@ -1004,35 +928,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05043702845977172</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>catboost</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.8478313400198138</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.01592899719276268</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3715476012769358</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.05069068522929388</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
   </sheetData>

--- a/results/05_modeling/ALL_summary.xlsx
+++ b/results/05_modeling/ALL_summary.xlsx
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7914604990850014</v>
+        <v>0.7950423734525505</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7638655851081998</v>
+        <v>0.778291616922111</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8102974592286788</v>
+        <v>0.8124041670509727</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -539,10 +539,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8665735005647537</v>
+        <v>0.8635755888181507</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7830138502042437</v>
+        <v>0.7827777918629683</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01871381086800399</v>
+        <v>0.01875913928122007</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1269362344566973</v>
+        <v>0.127235033139615</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03004361656874081</v>
+        <v>0.03014154041782496</v>
       </c>
     </row>
     <row r="3">
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7914604990850014</v>
+        <v>0.7950423734525505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02177196714317657</v>
+        <v>0.022906276421525</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1983569539223893</v>
+        <v>0.1921294753460224</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0418411119299538</v>
+        <v>0.04173421597947816</v>
       </c>
     </row>
   </sheetData>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7371297104138026</v>
+        <v>0.7416451769600094</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02055176014088759</v>
+        <v>0.01993688661995984</v>
       </c>
       <c r="D2" t="n">
-        <v>0.113979645704231</v>
+        <v>0.1154322800342247</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01327209032282319</v>
+        <v>0.01432159611287153</v>
       </c>
     </row>
     <row r="3">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7638655851081998</v>
+        <v>0.778291616922111</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01830461526364529</v>
+        <v>0.02016460778089968</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1305084174604524</v>
+        <v>0.1366611393084907</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01322728173796852</v>
+        <v>0.01644375607216518</v>
       </c>
     </row>
   </sheetData>
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7423180768872754</v>
+        <v>0.740204074741885</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01740707860779314</v>
+        <v>0.01632377788364275</v>
       </c>
       <c r="D2" t="n">
-        <v>0.150418939148557</v>
+        <v>0.1504672166943709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01096860461154251</v>
+        <v>0.01174477485781384</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8102974592286788</v>
+        <v>0.8124041670509727</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008404306776686604</v>
+        <v>0.00960631081931577</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2163882894451978</v>
+        <v>0.2179801169523388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01225359127876926</v>
+        <v>0.01386992304711891</v>
       </c>
     </row>
   </sheetData>
@@ -909,16 +909,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8384060741259433</v>
+        <v>0.8380082807867801</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02144293790929938</v>
+        <v>0.02096671842468235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3621556760174849</v>
+        <v>0.3626783404222963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03892340905464424</v>
+        <v>0.036706105017073</v>
       </c>
     </row>
     <row r="3">
@@ -928,16 +928,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8665735005647537</v>
+        <v>0.8635755888181507</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008279770287604037</v>
+        <v>0.007267449988741658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4183159022170709</v>
+        <v>0.4197146136049616</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05664601097712555</v>
+        <v>0.05043702845977172</v>
       </c>
     </row>
   </sheetData>
